--- a/artfynd/A 47560-2024 artfynd.xlsx
+++ b/artfynd/A 47560-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -925,6 +925,1150 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120610245</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rödflon, Rödflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>509082</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6984031</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120596337</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rödflon, Rödflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>509062</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6984171</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120596521</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rödflon, Rödflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>509056</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6984158</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120596300</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rödflon, Rödflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>509056</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6984193</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120603044</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rödflon, Rödflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>509088</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6984018</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120596433</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rödflon, Rödflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>509035</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6984198</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120596199</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rödflon, Rödflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>509047</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6984236</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120609703</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rödflon, Rödflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>509078</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6984030</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120596352</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rödflon, Rödflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>509060</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6984187</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120612362</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rödflon, Rödflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>509027</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6984049</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47560-2024 artfynd.xlsx
+++ b/artfynd/A 47560-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119290848</v>
+        <v>120596109</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rödflon, Rödflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509153</v>
+        <v>509071</v>
       </c>
       <c r="R2" t="n">
-        <v>6983863</v>
+        <v>6984239</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,22 +743,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -801,64 +786,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119291007</v>
+        <v>120596337</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rödflon, Rödflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509160</v>
+        <v>509062</v>
       </c>
       <c r="R3" t="n">
-        <v>6983879</v>
+        <v>6984171</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,22 +854,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,6 +878,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -927,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120596337</v>
+        <v>120596352</v>
       </c>
       <c r="B4" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509062</v>
+        <v>509060</v>
       </c>
       <c r="R4" t="n">
-        <v>6984171</v>
+        <v>6984187</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +970,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1015,7 +980,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,15 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120596433</v>
+        <v>120596521</v>
       </c>
       <c r="B5" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1086,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509035</v>
+        <v>509056</v>
       </c>
       <c r="R5" t="n">
-        <v>6984198</v>
+        <v>6984158</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,15 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120596199</v>
+        <v>120610245</v>
       </c>
       <c r="B6" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1199,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509047</v>
+        <v>509082</v>
       </c>
       <c r="R6" t="n">
-        <v>6984236</v>
+        <v>6984031</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,15 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120612362</v>
+        <v>120662468</v>
       </c>
       <c r="B7" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,37 +1237,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rödflon, Rödflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509027</v>
+        <v>509045</v>
       </c>
       <c r="R7" t="n">
-        <v>6984049</v>
+        <v>6984204</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,22 +1291,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,7 +1315,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1387,37 +1333,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120596352</v>
+        <v>120596300</v>
       </c>
       <c r="B8" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1430,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509060</v>
+        <v>509056</v>
       </c>
       <c r="R8" t="n">
-        <v>6984187</v>
+        <v>6984193</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1475,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,37 +1444,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120596521</v>
+        <v>120596433</v>
       </c>
       <c r="B9" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1546,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509056</v>
+        <v>509035</v>
       </c>
       <c r="R9" t="n">
-        <v>6984158</v>
+        <v>6984198</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,7 +1517,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1591,7 +1527,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,50 +1555,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120603044</v>
+        <v>120612362</v>
       </c>
       <c r="B10" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rödflon, Rödflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509088</v>
+        <v>509027</v>
       </c>
       <c r="R10" t="n">
-        <v>6984018</v>
+        <v>6984049</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1694,7 +1628,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1704,7 +1638,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,6 +1647,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1731,37 +1666,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120609703</v>
+        <v>120661298</v>
       </c>
       <c r="B11" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1771,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509078</v>
+        <v>509128</v>
       </c>
       <c r="R11" t="n">
-        <v>6984030</v>
+        <v>6983998</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,22 +1731,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,37 +1773,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120610245</v>
+        <v>120661894</v>
       </c>
       <c r="B12" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1883,10 +1808,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509082</v>
+        <v>509058</v>
       </c>
       <c r="R12" t="n">
-        <v>6984031</v>
+        <v>6984060</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,22 +1838,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,15 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120596300</v>
+        <v>120596199</v>
       </c>
       <c r="B13" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,37 +1891,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rödflon, Rödflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509056</v>
+        <v>509047</v>
       </c>
       <c r="R13" t="n">
-        <v>6984193</v>
+        <v>6984236</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2033,7 +1950,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2043,7 +1960,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,7 +1969,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2071,15 +1987,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120661894</v>
+        <v>120596475</v>
       </c>
       <c r="B14" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,21 +1998,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2111,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509058</v>
+        <v>509016</v>
       </c>
       <c r="R14" t="n">
-        <v>6984060</v>
+        <v>6984216</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2141,22 +2052,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,15 +2094,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120661572</v>
+        <v>120603044</v>
       </c>
       <c r="B15" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,37 +2105,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rödflon, Rödflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509112</v>
+        <v>509088</v>
       </c>
       <c r="R15" t="n">
-        <v>6984001</v>
+        <v>6984018</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2256,22 +2159,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,7 +2183,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2299,59 +2201,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120660358</v>
+        <v>120609703</v>
       </c>
       <c r="B16" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rödflon, Rödflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509130</v>
+        <v>509078</v>
       </c>
       <c r="R16" t="n">
-        <v>6983885</v>
+        <v>6984030</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2378,22 +2266,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,50 +2308,59 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120662468</v>
+        <v>119290848</v>
       </c>
       <c r="B17" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rödflon, Rödflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509045</v>
+        <v>509153</v>
       </c>
       <c r="R17" t="n">
-        <v>6984204</v>
+        <v>6983863</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2490,22 +2387,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2532,15 +2429,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120661816</v>
+        <v>119291007</v>
       </c>
       <c r="B18" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2567,7 +2459,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2575,16 +2467,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rödflon, Rödflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509083</v>
+        <v>509160</v>
       </c>
       <c r="R18" t="n">
-        <v>6984087</v>
+        <v>6983879</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2611,22 +2508,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2653,50 +2550,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120658893</v>
+        <v>120660305</v>
       </c>
       <c r="B19" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rödflon, Rödflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509073</v>
+        <v>509146</v>
       </c>
       <c r="R19" t="n">
-        <v>6983885</v>
+        <v>6983895</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2728,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2738,7 +2639,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2765,15 +2666,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120660305</v>
+        <v>120660358</v>
       </c>
       <c r="B20" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2800,7 +2696,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2814,10 +2710,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509146</v>
+        <v>509130</v>
       </c>
       <c r="R20" t="n">
-        <v>6983895</v>
+        <v>6983885</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2849,7 +2745,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2859,7 +2755,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2886,53 +2782,60 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120661298</v>
+        <v>120660681</v>
       </c>
       <c r="B21" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rödflon, Rödflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509128</v>
+        <v>509174</v>
       </c>
       <c r="R21" t="n">
-        <v>6983998</v>
+        <v>6983915</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2961,7 +2864,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2971,7 +2874,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2980,6 +2883,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2998,15 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120661874</v>
+        <v>120661816</v>
       </c>
       <c r="B22" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3033,7 +2932,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3047,13 +2946,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509085</v>
+        <v>509083</v>
       </c>
       <c r="R22" t="n">
-        <v>6984042</v>
+        <v>6984087</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3082,7 +2981,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3092,7 +2991,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3116,6 +3015,243 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120661874</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Rödflon, Rödflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>509085</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6984042</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134413981</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Rödflon, Rödflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>509198</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6983850</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47560-2024 artfynd.xlsx
+++ b/artfynd/A 47560-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596109</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596337</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596352</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596521</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120610245</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1330,6 +1360,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120662468</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596300</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,6 +1592,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596433</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1663,6 +1708,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120612362</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1770,6 +1820,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120661298</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1877,6 +1932,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120661894</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1984,6 +2044,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596199</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2091,6 +2156,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596475</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2198,6 +2268,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120603044</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2305,6 +2380,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120609703</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2426,6 +2506,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119290848</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2547,6 +2632,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119291007</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2663,6 +2753,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120660305</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2779,6 +2874,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120660358</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2899,6 +2999,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120660681</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3015,6 +3120,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120661816</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3131,6 +3241,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120661874</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3252,8 +3367,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134413981</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>